--- a/artfynd/A 3927-2022 artfynd.xlsx
+++ b/artfynd/A 3927-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3927-2022 artfynd.xlsx
+++ b/artfynd/A 3927-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,65 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99568603</v>
+        <v>95296090</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Spillkrakan, Nrk</t>
+          <t>Sandbacken Ö, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489265.2615907325</v>
+        <v>489282</v>
       </c>
       <c r="R2" t="n">
-        <v>6521261.965684538</v>
+        <v>6521247</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-03-31</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:29</t>
+          <t>2021-08-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-03-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:29</t>
+          <t>2021-08-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lovisa Larsson</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lovisa Larsson</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104656631</v>
+        <v>113657504</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,34 +783,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skogarna runt Norra Bocksjön, Nrk</t>
+          <t>Stora Björstorp, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489195.249895424</v>
+        <v>489255</v>
       </c>
       <c r="R3" t="n">
-        <v>6521263.196115711</v>
+        <v>6521150</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,27 +841,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Precis i kanten mot mer brukad skog.</t>
+          <t>Några fläckar på block i nordvänd, mindre brant.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,71 +860,67 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104656630</v>
+        <v>95492715</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogarna runt Norra Bocksjön, Nrk</t>
+          <t>Sandbacken Ö, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489263.5978822075</v>
+        <v>489297</v>
       </c>
       <c r="R4" t="n">
-        <v>6521223.142911152</v>
+        <v>6521241</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,27 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-03-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Måttligt mycket</t>
+          <t>2021-03-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,27 +964,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Sebastian Kirppu, Lovisa Larsson, David Tverling</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Miniforskningsresan Extensus Örebro län 2021</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113503512</v>
+        <v>95492713</v>
       </c>
       <c r="B5" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,49 +991,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>6428</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stora Björstorp, Nrk</t>
+          <t>Sandbacken Ö, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489205</v>
+        <v>489306</v>
       </c>
       <c r="R5" t="n">
-        <v>6521318</v>
+        <v>6521247</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,22 +1045,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-05-06</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2021-03-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-05-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2021-03-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,27 +1065,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Sebastian Kirppu, Lovisa Larsson, David Tverling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Miniforskningsresan Extensus Örebro län 2021</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113657701</v>
+        <v>98286740</v>
       </c>
       <c r="B6" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,43 +1092,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stora Björstorp, Nrk</t>
+          <t>Norra Bocksjön, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489160</v>
+        <v>489268</v>
       </c>
       <c r="R6" t="n">
-        <v>6521255</v>
+        <v>6521322</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1236,17 +1154,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ganska mycket spår. I död gran i sumpskogskant.</t>
+          <t>gamla hackmärken</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,34 +1173,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113503493</v>
+        <v>99568603</v>
       </c>
       <c r="B7" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,45 +1202,49 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stora Björstorp, Nrk</t>
+          <t>Spillkrakan, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489205</v>
+        <v>489265</v>
       </c>
       <c r="R7" t="n">
-        <v>6521318</v>
+        <v>6521262</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1352,17 +1268,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-05-06</t>
+          <t>2022-03-31</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-05-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Under tall, från vinterhalvåret.</t>
+          <t>2022-03-31</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,15 +1298,1358 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Lovisa Larsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lovisa Larsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>95296091</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sandbacken Ö, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>489204</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6521255</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>95492719</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sandbacken Ö, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>489236</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6521310</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-03-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-03-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu, Lovisa Larsson, David Tverling</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Miniforskningsresan Extensus Örebro län 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113503493</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stora Björstorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>489205</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6521318</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-05-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-05-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Under tall, från vinterhalvåret.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Lars Gerre</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Lars Gerre</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>113657701</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stora Björstorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>489160</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6521255</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-04-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-04-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ganska mycket spår. I död gran i sumpskogskant.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>113503512</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stora Björstorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>489205</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6521318</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-05-06</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-05-06</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>95296092</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sandbacken Ö, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>489119</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6521263</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>95296089</v>
+      </c>
+      <c r="B14" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sandbacken Ö, Nrk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>489281</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6521266</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>104231005</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skogarna runt Norra Bocksjön, Nrk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>489107</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6521193</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-03-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-03-25</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Inte så mycket och i sämre skick</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>104656627</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skogarna runt Norra Bocksjön, Nrk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>489301</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6521251</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Mycket</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>104656630</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skogarna runt Norra Bocksjön, Nrk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>489264</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6521223</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Måttligt mycket</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>104656631</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skogarna runt Norra Bocksjön, Nrk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>489195</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6521263</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Precis i kanten mot mer brukad skog.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>95492711</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sandbacken Ö, Nrk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>489299</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6521229</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2021-03-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2021-03-16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu, Lovisa Larsson, David Tverling</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Miniforskningsresan Extensus Örebro län 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>95492712</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sandbacken Ö, Nrk</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>489314</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6521245</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2021-03-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2021-03-16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu, Lovisa Larsson, David Tverling</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Miniforskningsresan Extensus Örebro län 2021</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3927-2022 artfynd.xlsx
+++ b/artfynd/A 3927-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95296090</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113657504</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
           <t>Miniforskningsresan Extensus Örebro län 2021</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95492715</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
           <t>Miniforskningsresan Extensus Örebro län 2021</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95492713</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1188,6 +1213,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98286740</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1307,6 +1337,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99568603</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1404,6 +1439,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95296091</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1505,6 +1545,11 @@
           <t>Miniforskningsresan Extensus Örebro län 2021</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95492719</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1615,6 +1660,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113503493</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1727,6 +1777,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113657701</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1846,6 +1901,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113503512</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1943,6 +2003,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95296092</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2040,6 +2105,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95296089</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2142,6 +2212,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104231005</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2244,6 +2319,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104656627</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2346,6 +2426,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104656630</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2448,6 +2533,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104656631</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2549,6 +2639,11 @@
           <t>Miniforskningsresan Extensus Örebro län 2021</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95492711</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2650,8 +2745,34 @@
           <t>Miniforskningsresan Extensus Örebro län 2021</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95492712</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>